--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0092.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0092.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Domain - Malfunction</t>
+          <t>Tổ Tacet - Lỗi Hệ Thống</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Domain - Barrier</t>
+          <t>Tổ Tacet - Rào Chắn</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Passive - Reversal</t>
+          <t>Thụ Động - Đảo Ngược</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Passive - Burn</t>
+          <t>Thụ Động - Thiêu Đốt</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Passive - Adaptation</t>
+          <t>Thụ Động - Thích Ứng</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Passive - Invisibility</t>
+          <t>Thụ Động - Tàng Hình</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Passive - Fortified</t>
+          <t>Thụ Động - Củng Cố</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Passive - Bounty</t>
+          <t>Thụ Động - Tiền Thưởng</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Cần trang bị ít nhất một Vũ khí của KU-Roro</t>
+          <t>Ít nhất phải trang bị một Vũ Khí KU-Roro</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Không thể trang bị thêm Vũ khí của KU-Roro</t>
+          <t>Không thể trang bị thêm Vũ Khí KU-Roro</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Mở khóa mô phỏng mới</t>
+          <t>Mô phỏng mới đã mở khóa</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Tactic Set</t>
+          <t>Bộ Chiến Thuật</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Machine Equipped</t>
+          <t>Thiết bị đã được trang bị</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Chop Chop: Headless</t>
+          <t>Chop Chop: Không Đầu</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Nimbus Wraith</t>
+          <t>Hồn Ma Nimbus</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Electro Predator</t>
+          <t>Thú Điện Khát Máu</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Aero Predator</t>
+          <t>Thú Dữ Gió</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Chop Chop</t>
+          <t>Nhanh lên nào</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Lumiscale Construct</t>
+          <t>Cấu Trúc Vảy Quang</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Không Traits</t>
+          <t>Không có Thuộc tính</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Không Traits</t>
+          <t>Không có Thuộc tính</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Không Traits</t>
+          <t>Không có Thuộc tính</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Tiêu Chuẩn Tacet Discords</t>
+          <t>Tacet Discord tiêu chuẩn</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Elite Tacet Discords</t>
+          <t>Tacet Discord Cấp Tinh Anh</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Dangerous Tacet Discords</t>
+          <t>Những Tacet Discord nguy hiểm</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Nhỏ</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Trung bình</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>Cỡ lớn</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Universal Tactics</t>
+          <t>Chiến Thuật Chung</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Saturation Fire</t>
+          <t>Lửa Bão Hòa</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Silver Bullet</t>
+          <t>Đạn Bạc</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Echo Synergy</t>
+          <t>Đồng Bộ Tiếng Vọng</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Flamebound</t>
+          <t>Gắn Bó Với Lửa</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Silent Lightning</t>
+          <t>Tia Chớp Vô Thanh</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Superconductor</t>
+          <t>Chất Siêu Dẫn</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Overflow Discharge</t>
+          <t>Giải Phóng Tràn Đầy</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Inductive Shock</t>
+          <t>Sốc Cảm Ứng</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Static Breach</t>
+          <t>Xâm Nhập Tĩnh</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Chain Thunder</t>
+          <t>Sấm Sét Dây Xích</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Darting Bolt</t>
+          <t>Mũi Tên Phóng</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Lightning Chain</t>
+          <t>Sét Liên Hoàn</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Weakened Resistance</t>
+          <t>Kháng Cự Suy Yếu</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Static Suppression</t>
+          <t>Ức Chế Tĩnh</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Superconductor</t>
+          <t>Chất Siêu Dẫn</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Overflow Discharge</t>
+          <t>Giải Phóng Tràn Đầy</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Inductive Shock</t>
+          <t>Sốc Cảm Ứng</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Static Breach</t>
+          <t>Xâm Nhập Tĩnh</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Chain Thunder</t>
+          <t>Sấm Sét Dây Xích</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Darting Bolt</t>
+          <t>Mũi Tên Phóng</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Lightning Chain</t>
+          <t>Sét Liên Hoàn</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Weakened Resistance</t>
+          <t>Kháng Cự Suy Yếu</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Static Suppression</t>
+          <t>Ức Chế Tĩnh</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Tacetite Spikes</t>
+          <t>Gai Tổ Tacet</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Hologram Echo: Drake</t>
+          <t>Hồi Âm Hologram: Drake</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Glacio Beacon</t>
+          <t>Đèn Hiệu Glacio</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Stun Emitter</t>
+          <t>Bộ Phát Choáng</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Glitch Spawner</t>
+          <t>Lồng Nuôi Lỗi</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Hologram Echo: Junrock</t>
+          <t>Hồi Âm Hologram: Junrock</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Thunder Lance</t>
+          <t>Lôi Thương</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Tacetite Barrage</t>
+          <t>Bão Tacetite</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Frost Spout</t>
+          <t>Cột băng phun trào</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Repulsor Spout</t>
+          <t>Vòi Phun Đẩy</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Vortex Generator</t>
+          <t>Máy Phát Xoáy Lốc</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Hologram Echo: Hoartoise</t>
+          <t>Hồi Âm Hologram: Hoartoise</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Shock Inductor</t>
+          <t>Bộ Cảm Ứng Sốc</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Whirlpool Device</t>
+          <t>Thiết Bị Vực Xoáy</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Freeze Jet</t>
+          <t>Tia Đông Cứng</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Hologram Echo: Puff</t>
+          <t>Hồi Âm Hologram: Puff</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Hologram Echo: Chest Mimic</t>
+          <t>Hồi Âm Hologram: Quái Giả Hòm Kho Báu</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Burst Launcher</t>
+          <t>Bộ Phát Kích Hoạt</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Speed Shooter</t>
+          <t>Xạ Thủ Tốc Độ</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Plasma Cannon</t>
+          <t>Pháo Plasma</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Repulsion Field</t>
+          <t>Trường Đẩy Lùi</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Stagnation Field</t>
+          <t>Vùng Trì Trệ</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Khiên</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Healing</t>
+          <t>Hồi Phục</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Tốc độ di chuyển</t>
+          <t>Tốc Độ Di Chuyển</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Frequency Neutralizer</t>
+          <t>Bộ Trung Hòa Tần Số</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Freezing Pulse</t>
+          <t>Xung Lạnh Đóng Băng</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Shock Pulse</t>
+          <t>Xung Kích Điện</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Matrix Command: Modulation</t>
+          <t>Lệnh Ma trận: Modulation</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Weapon Nâng cấp</t>
+          <t>Nâng Cấp Vũ Khí</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Amplifier Beacon</t>
+          <t>Đèn Tín Hiệu Khuếch Đại</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Magma Pulse</t>
+          <t>Xung Nhiệt Dung Nham</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Matrix Command: Overload</t>
+          <t>Lệnh Ma trận: Quá Tải</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Đã Đạt Cấp Độ Tối Đa</t>
+          <t>Đã đạt Giới hạn Cấp độ</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Venture Capital Fund I</t>
+          <t>Quỹ Đầu Tư Mạo Hiểm I</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Database Expansion I</t>
+          <t>Giai Đoạn Mở Rộng Kho Dữ Liệu I</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Venture Capital Fund II</t>
+          <t>Quỹ Đầu Tư Mạo Hiểm II</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Database Expansion II</t>
+          <t>Giai Đoạn Mở Rộng Kho Dữ Liệu II</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Link Optimization I</t>
+          <t>Tối Ưu Hóa Liên Kết I</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Device Nâng cấp Plan I</t>
+          <t>Gói Nâng cấp Thiết bị I</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Venture Capital Fund III</t>
+          <t>Quỹ Đầu Tư Mạo Hiểm III</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Insider Trading Intel I</t>
+          <t>Tình Báo Giao Dịch Nội Gián I</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Database Expansion III</t>
+          <t>Giai Đoạn Mở Rộng Kho Dữ Liệu III</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Link Optimization II</t>
+          <t>Tối Ưu Hóa Liên Kết II</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Device Nâng cấp Plan II</t>
+          <t>Gói Nâng cấp Thiết bị II</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Insider Trading Intel II</t>
+          <t>Tình Báo Giao Dịch Nội Gián II</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Insider Trading Intel III</t>
+          <t>Tình Báo Giao Dịch Nội Gián III</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Weapon Nâng cấp: Firepower</t>
+          <t>Nâng Cấp Vũ Khí: Hỏa Lực</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Weapon Nâng cấp: Suppression</t>
+          <t>Nâng Cấp Vũ Khí: Áp Chế</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Database Expansion IV</t>
+          <t>Giai Đoạn Mở Rộng Kho Dữ Liệu IV</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Link Optimization III</t>
+          <t>Tối Ưu Hóa Liên Kết III</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Weapon Nâng cấp Plan</t>
+          <t>Kế Hoạch Nâng Cấp Vũ Khí</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Armory Expansion</t>
+          <t>Mở Rộng Kho Trang Bị</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Weakness Analysis</t>
+          <t>Phân Tích Điểm Yếu</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Database Expansion V</t>
+          <t>Giai Đoạn Mở Rộng Kho Dữ Liệu V</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Link Optimization IV</t>
+          <t>Tối Ưu Hóa Liên Kết IV</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Device Augmentation</t>
+          <t>Tăng cường Thiết bị</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Tactic Revision</t>
+          <t>Điều Chỉnh Chiến Thuật</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Logistics Assurance</t>
+          <t>Bảo Đảm Hậu Cần</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Weakness Targeting I</t>
+          <t>Nhắm Mục Tiêu Yếu I</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Weakness Targeting II</t>
+          <t>Nhắm Mục Tiêu Yếu II</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Defense Readiness</t>
+          <t>Sẵn Sàng Phòng Ngự</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Vượt Qua Giới Hạn</t>
+          <t>Vượt Qua Biên Giới</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Hãy mở khóa Protocol điều kiện trước</t>
+          <t>Hãy mở khóa Giao Thức tiên quyết trước</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Protocol Unlocked</t>
+          <t>Giao Thức Đã Mở Khóa</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Kỷ lục cao nhất</t>
+          <t>Kỷ Lục Cao Nhất</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Featured Event</t>
+          <t>Sự Kiện Nổi Bật</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Mô phỏng Phòng thủ Thủy triều</t>
+          <t>Mô Phỏng Phòng Thủ Thủy Triều</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Special Vật phẩm</t>
+          <t>Vật Phẩm Đặc Biệt</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Chiến thuật</t>
+          <t>Chiến Thuật</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Refreshed</t>
+          <t>Đã làm mới</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Elite Tacet Discords sắp xuất hiện</t>
+          <t>Tacet Discord tinh nhuệ sắp xuất hiện</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Chế độ Deathtrap không khả dụng</t>
+          <t>Chế Độ Bẫy Chết chưa khả dụng</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Tăng Cường Kỹ Thuật</t>
+          <t>Tăng cường Kỹ thuật</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Làn sóng hiện tại</t>
+          <t>Làn Sóng Hiện Tại</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Enhancement Overview</t>
+          <t>Tổng Quan Nâng Cấp</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Insufficient Sim Ingots</t>
+          <t>Không đủ Thỏi Sim</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Đây không phải môi trường Tidal Defense Simulator</t>
+          <t>Đây không phải là môi trường mô phỏng Phòng Thủ Thủy Triều.</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Không thể chọn ngẫu nhiên Tactic Set trong Deathtrap Mode</t>
+          <t>Không chọn ngẫu nhiên được Bộ Chiến Thuật trong Chế Độ Bẫy Tử Thần</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Cấu hình Tactic Set không tồn tại trong Deathtrap Mode</t>
+          <t>Cấu hình Bộ Chiến Thuật không tồn tại trong Chế Độ Bẫy Chết</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Cấu hình Tactic không tồn tại trong Deathtrap Mode</t>
+          <t>Cấu hình Chiến Thuật không tồn tại trong Chế Độ Bẫy Chết</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Không thể ngẫu nhiên hóa độ hiếm của Tactic trong Deathtrap Mode</t>
+          <t>Không ngẫu nhiên được độ hiếm Chiến Thuật trong Chế Độ Bẫy Tử Thần</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Không thể chọn ngẫu nhiên Tactic Set trong Deathtrap Mode</t>
+          <t>Không chọn ngẫu nhiên được Bộ Chiến Thuật trong Chế Độ Bẫy Tử Thần</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Nhóm Tactic ngẫu nhiên trong Deathtrap Mode đang trống</t>
+          <t>Bể chiến thuật ngẫu nhiên trong Chế Độ Bẫy Chết đang trống</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Không có Tactic Set khả dụng để rút Tactic trong Deathtrap Mode</t>
+          <t>Không có Bộ Chiến Thuật nào để rút Chiến Thuật trong Chế Độ Bẫy Chết</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Không có độ hiếm khả dụng để rút Tactic trong Deathtrap Mode</t>
+          <t>Không có độ hiếm nào khả dụng để rút Chiến Thuật trong Chế Độ Bẫy Tử Thần</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Hành vi rút Tactic trong Deathtrap Mode chưa được cấu hình</t>
+          <t>Hành vi rút Chiến Thuật trong Chế Độ Bẫy Tử vẫn chưa được cấu hình</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Tacet Discord Wave chưa được cấu hình</t>
+          <t>Sóng Tacet Discord Chưa Được Cấu Hình</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Preparation phase wave chưa được cấu hình</t>
+          <t>Lượt chuẩn bị chưa được thiết lập</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Dữ liệu Tacet Discord trùng lặp trong wave</t>
+          <t>Dữ liệu Tacet Discord trùng lặp trong đợt sóng</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Combat Machine chưa được cấu hình</t>
+          <t>Máy Chiến Đấu chưa cấu hình</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Không tìm thấy thực thể Combat Machine trong hệ thống lưới</t>
+          <t>Không tìm thấy thực thể Máy Chiến Đấu trong hệ thống lưới</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Bạn không ở trong giai đoạn Chuẩn bị</t>
+          <t>Ngươi chưa vào giai đoạn Chuẩn Bị</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Chưa thiết lập Bộ Chiến thuật</t>
+          <t>Bộ Chiến Thuật Chưa Được Cấu Hình</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Danh sách Bộ Chiến thuật ngẫu nhiên đã thiết lập trống</t>
+          <t>Danh sách Chiến Thuật ngẫu nhiên đã thiết lập đang trống</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Danh sách độ hiếm ngẫu nhiên đã thiết lập trống</t>
+          <t>Danh sách Độ Hiếm ngẫu nhiên đã thiết lập đang trống</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Tham số truy vấn bị trùng lặp</t>
+          <t>Tham số truy vấn trùng lặp</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Chưa đến thời gian nhận phần thưởng</t>
+          <t>Chưa phải lúc nhận thưởng đâu.</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Chưa đáp ứng điều kiện</t>
+          <t>Điều kiện chưa được đáp ứng</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Không ở trong phiên bản sự kiện</t>
+          <t>Không trong phiên bản sự kiện</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Môi trường Mô phỏng Phòng thủ Thủy triều chưa được cấu hình</t>
+          <t>Môi trường Mô phỏng Phòng thủ Thủy Triều chưa được cấu hình</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Giai đoạn này đang bị khóa</t>
+          <t>Giai đoạn này đã bị khóa.</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Combat Machine này đang bị khóa</t>
+          <t>Máy Chiến Đấu này đang bị khóa.</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Không thể trang bị lại cùng một Combat Machine</t>
+          <t>Không thể trang bị lại cùng một Chiến Dịch Cơ Giới</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Không thể yêu cầu lại cùng một Combat Machine</t>
+          <t>Không thể yêu cầu lại cùng một Chiến Dịch Cơ Giới</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Combat Machine chưa được cấu hình</t>
+          <t>Máy Chiến Đấu chưa cấu hình</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Vũ khí của KU-Roro chưa được cấu hình</t>
+          <t>Vũ khí của KU-Roro chưa được thiết lập</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Không thể trang bị lại cùng một vũ khí của KU-Roro</t>
+          <t>Không thể trang bị lại cùng một Vũ Khí KU-Roro</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Chưa trang bị Combat Machine cần thiết</t>
+          <t>Chưa trang bị Máy Chiến Đấu Cần Thiết</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Chưa trang bị vũ khí của KU-Roro cần thiết</t>
+          <t>Chưa trang bị Vũ Khí KU-Roro Cần Thiết</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Cấp độ Combat Machine chưa được cấu hình</t>
+          <t>Mức độ Máy Chiến Đấu chưa cấu hình</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Cỗ Máy Chiến Đấu đã đạt cấp cao nhất</t>
+          <t>Cỗ Máy Chiến Đấu đã đạt đến cấp độ tối thượng.</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Thiếu cấu hình sự kiện</t>
+          <t>Thiếu cấu hình sự kiện.</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Không có cấu hình cấp độ Vũ khí của KU-Roro</t>
+          <t>Cấp độ Vũ khí của KU-Roro chưa được thiết lập</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Vũ khí của KU-Roro đã đạt cấp cao nhất</t>
+          <t>Vũ khí của KU-Roro đã đạt cấp độ cao nhất</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Không có lựa chọn hiện tại cho Vũ khí của KU-Roro</t>
+          <t>Hiện không có tùy chọn cho Vũ Khí KU-Roro</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Không có lựa chọn hiện tại cho Cỗ Máy Chiến Đấu</t>
+          <t>Hiện không có tùy chọn cho Chiến Dịch Cơ Giới</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Thao tác đặt lại Vũ khí của KU-Roro không hợp lệ</t>
+          <t>Hành động đặt lại của Vũ Khí KU-Roro không hợp lệ</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Thao tác đặt lại Cỗ Máy Chiến Đấu không hợp lệ</t>
+          <t>Hành động đặt lại của Combat Machine không hợp lệ</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Thiếu cấu hình Giao Thức Giám Sát</t>
+          <t>Thiếu cấu hình Giao thức Giám sát</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Thiếu cấu hình Giao Thức Giám Sát</t>
+          <t>Thiếu cấu hình Giao thức Giám sát</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Giao Thức Tiền Điều Kiện chưa được kích hoạt</t>
+          <t>Giao thức Điều kiện tiên quyết chưa được kích hoạt</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Insufficient Rating Stars</t>
+          <t>Sao đánh giá không đủ</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Insufficient Sim Creditss</t>
+          <t>Không đủ Tín Dụng Sim</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Kho vật phẩm không đủ</t>
+          <t>Kho đồ không đủ chỗ</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Không phải thực thể Sim Credit</t>
+          <t>Không phải thực thể Tín Dụng Sim đâu.</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Không phải thực thể Tacet Discord</t>
+          <t>Không phải thực thể Tacet Discord đâu.</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Không phải thực thể Combat Machine</t>
+          <t>Không phải thực thể Chiến Cỗ Máy đâu.</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Tất cả biến số không thể giảm dưới 0</t>
+          <t>Không biến số nào được phép xuống dưới 0</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Thiếu tất cả loại biến số</t>
+          <t>Tất cả các loại biến số đều bị thiếu</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Tactic đã bán</t>
+          <t>Chiến thuật đã chọn đã được bán.</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Đã đạt giới hạn triển khai Combat Machine</t>
+          <t>Đã đạt giới hạn triển khai Máy Chiến Đấu</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Không ở giai đoạn nhận thưởng</t>
+          <t>Chưa đến giai đoạn nhận thưởng</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Thiếu dữ liệu để vẽ Tactics.</t>
+          <t>Thiếu dữ liệu để vẽ Chiến Thuật.</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Đã hết lượt làm mới để rút Tactics.</t>
+          <t>Đã hết lượt làm mới để rút Chiến Thuật.</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Chưa cấu hình khu vực đặc biệt</t>
+          <t>Khu vực đặc biệt chưa được cấu hình</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Chưa cấu hình khu vực đặc biệt cấp độ cụ thể</t>
+          <t>Khu vực đặc biệt cấp độ cụ thể chưa được cấu hình</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Insufficient Frequency Neutralizers</t>
+          <t>Bộ Trung Hòa Tần số không đủ</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Loại khu vực đặc biệt không khớp</t>
+          <t>Loại khu vực đặc biệt vô đối</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Không phải khu vực đặc biệt trong Tidal Defense Simulator</t>
+          <t>Không phải khu vực đặc biệt trong Mô phỏng Phòng thủ Thủy triều</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Combat Machine không thể bị phá hủy</t>
+          <t>Máy Chiến Đấu không thể bị phá hủy</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Kết quả rút Tactic trống</t>
+          <t>Kết Quả Rút Chiến Thuật Trống</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Tactic đã đạt cấp cao nhất</t>
+          <t>Chiến Thuật đã đạt cấp độ cao nhất</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Độ bền Energy Matrix không thể cạn kiệt</t>
+          <t>Độ Bền Ma Trận Năng Lượng không thể cạn kiệt</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Mô Phỏng Hoàn Tất</t>
+          <t>Hoàn Thành Mô Phỏng</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Mô Phỏng Hoàn Tất</t>
+          <t>Hoàn Thành Mô Phỏng</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Tham gia sự kiện để mở khóa Flight Công cụ</t>
+          <t>Tham gia sự kiện để mở khóa tính năng Bay.</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Flight Công cụ hiện đã có sẵn tại Jinzhou</t>
+          <t>Chức Năng Bay đã mở khóa tại Jinzhou</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Săn mồi theo bầy</t>
+          <t>Săn theo bầy</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Tiến tới trận đấu tiếp theo</t>
+          <t>Tiếp tục trận đấu kế tiếp</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Mỏ khoáng đang chờ chiếm lấy</t>
+          <t>Mỏ Trong Tầm Tay</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Một luồng lửa bùng phát</t>
+          <t>Làn Lửa Bùng Nổ</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Hãy khiếp sợ trước Tiếng Gầm của Ta</t>
+          <t>Hãy run sợ dưới Tiếng Gầm Ta</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Erosive Wind</t>
+          <t>Gió Xói Mòn</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Tide Fall</t>
+          <t>Thủy Triều Rút</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Resoluteness</t>
+          <t>Kiên Định</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Rain Shower</t>
+          <t>Cơn Mưa Rào</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Breaking Wave</t>
+          <t>Phá Sóng Dữ</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Suggestion</t>
+          <t>Gợi ý</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Giấc Mơ Của Lửa Tro: Huyết</t>
+          <t>Giấc Mơ Của Tro Tàn: Huyết</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Giấc Mơ Của Lửa Tro: Cốt</t>
+          <t>Giấc Mơ Tro Tàn: Cốt</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Giấc Mơ Của Lửa Tro: Linh Hồn</t>
+          <t>Giấc Mơ Của Tro Tàn: Animus</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Giấc Mơ Của Lửa Tro: Đoạn Kết</t>
+          <t>Giấc Mơ Tro Tàn: Khúc Kết</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Đã mở khóa khu vực mới</t>
+          <t>Vùng đất mới đã mở khóa</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Blaze</t>
+          <t>Lửa Thiêu</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Hurricane</t>
+          <t>Bão Cuồng Phong</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Sấm Sét</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Blizzard</t>
+          <t>Bão Tuyết</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Spree</t>
+          <t>Điên Cuồng</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Spirit</t>
+          <t>Linh Khí</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Thời Gian</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Khiên</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Blaze - Magma</t>
+          <t>Blaze - Dung Nham</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Blaze - Crucible</t>
+          <t>Lửa Thiêu - Lò Luyện Tội</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Blaze - Inferno</t>
+          <t>Blaze - Hỏa Ngục</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Blaze - Wildfire</t>
+          <t>Blaze - Hỏa Tai</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Hurricane - Torrent</t>
+          <t>Bão Cuồng Phong - Dòng Chảy Xiết</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Hurricane - Cloudburst</t>
+          <t>Bão Cuồng Phong - Mưa Rào</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Hurricane - Downpour</t>
+          <t>Bão Cuồng Phong - Mưa Lớn</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Hurricane - Tsunami</t>
+          <t>Bão Cuồng Phong - Sóng Thần</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Thunder - Echobolt</t>
+          <t>Sấm Sét - Tia Vang</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Thunder - Skyflash</t>
+          <t>Sấm Sét - Tia Chớp Trời</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Thunder - Shockwave</t>
+          <t>Sấm Sét - Sóng Xung Kích</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Thunder - Wildvolt</t>
+          <t>Sấm Sét - Điện Hoang Dã</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Blizzard - Icebind</t>
+          <t>Bão Tuyết - Đông Cứng</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Blizzard - Snowlock</t>
+          <t>Bão Tuyết - Khóa Băng</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Blizzard - Coldbane</t>
+          <t>Bão Tuyết - Lạnh Cắt Da</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Blizzard - Frostend</t>
+          <t>Bão Tuyết - Sương Giá</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Spree - Ecstasy</t>
+          <t>Điên Cuồng - Sung Sướng</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Spree - Immersion</t>
+          <t>Đắm Chìm - Đắm Say</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Spree - Euphoria</t>
+          <t>Điên Cuồng - Phấn Khích</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Spree - Indulgence</t>
+          <t>Đắm Chìm - Thỏa Mãn</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Spirit - Focus</t>
+          <t>Linh Khí - Tập Trung</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Spirit - Mastery</t>
+          <t>Linh Khí - Thành Thạo</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Spirit - Ego</t>
+          <t>Linh Khí - Bản Ngã</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Spirit - Senses</t>
+          <t>Linh Khí - Giác Quan</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Time - Flow</t>
+          <t>Thời Gian - Dòng Chảy</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Time - Rift</t>
+          <t>Thời Gian - Vết Nứt</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Time - Stock</t>
+          <t>Thời Gian - Dự Trữ</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Time - Shift</t>
+          <t>Thời Gian - Dịch Chuyển</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Erosion - Mark</t>
+          <t>Xói Mòn - Dấu Ấn</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Erosion - Drench</t>
+          <t>Xói Mòn - Thấm Đẫm</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Erosion - Blow</t>
+          <t>Xói Mòn - Đòn Đánh</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Erosion - Spall</t>
+          <t>Xói Mòn - Bong Tróc</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Shield - Radiance</t>
+          <t>Khiên - Huy Hoàng</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Shield - Freedom</t>
+          <t>Khiên - Tự Do</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Shield - Juggernaut</t>
+          <t>Khiên - Bất Khuất</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Shield - Realm</t>
+          <t>Khiên - Cõi Giới</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Sấm Sét</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Blizzard</t>
+          <t>Bão Tuyết</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Spree</t>
+          <t>Điên Cuồng</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Spirit</t>
+          <t>Linh Khí</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Thời Gian</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Miễn Nhiễm Tử Vong</t>
+          <t>Miễn nhiễm với hiệu ứng Tử Vong</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Nhận Thưởng</t>
+          <t>Nhận thưởng</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Cleared</t>
+          <t>Hoàn thành giải trừ</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Render Options</t>
+          <t>Tùy Chọn Kết Xuất</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Dấu Ấn Hoang Dã</t>
+          <t>Dấu Vết Hoang Dã</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Dấu Ấn Hoang Dã</t>
+          <t>Dấu Vết Hoang Dã</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Compound Spring</t>
+          <t>Lò Xo Ghép</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Compound Gear</t>
+          <t>Bánh Răng Ghép</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Torridity Rescuer</t>
+          <t>Vị cứu tinh nhiệt huyết</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Timeworn Comb</t>
+          <t>Lược Cũ Mòn</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Pha Lê Mâu Thuẫn</t>
+          <t>Pha Lê Nghịch Lý</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Khát Khao Hủy Diệt</t>
+          <t>Khát Vọng Hủy Diệt</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Old Device I</t>
+          <t>Thiết Bị Cũ I</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Old Revolver</t>
+          <t>Khẩu Súng Lục Cũ</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Crude Nameplate</t>
+          <t>Bảng Tên Thô</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Emergency Call</t>
+          <t>Cuộc Gọi Khẩn Cấp</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Inferior Spring</t>
+          <t>Mùa Xuân Thấp Kém</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Petite Tacetite Bloom</t>
+          <t>Bông Tacetite Nhỏ</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Irregular Aromatherapy</t>
+          <t>Liệu Pháp Mùi Hương Bất Thường</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Guardian's Proof</t>
+          <t>Chứng Cứ Người Bảo Vệ</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Wonderland Phantasm</t>
+          <t>Ảo Ảnh Kỳ Diệu</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Medic Kit</t>
+          <t>Bộ Dụng Cụ Y Tế</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Phổ Biến Dạng</t>
+          <t>Phổ Bóp Méo</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Giấc Mơ Cao Nguyên</t>
+          <t>Giấc Mộng Cao Nguyên</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Compound Nut</t>
+          <t>Đai Ốc Ghép</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Risky Game</t>
+          <t>Trò chơi mạo hiểm</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Resounding Bell</t>
+          <t>Chuông Vang Dội</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Comb</t>
+          <t>Lược</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Mặt Trời Rực Cháy Trong Rừng</t>
+          <t>Mặt Trời Nóng Rực Trong Khu Rừng</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Old Device II</t>
+          <t>Thiết Bị Cũ II</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Soldier's Dog Tag</t>
+          <t>Thẻ bài của người lính</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Nameplate</t>
+          <t>Bảng tên</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Prisoner Unchained</t>
+          <t>Tù Nhân Được Giải Xiềng</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Mùa Xuân</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Tiêu Chuẩn Tacetite Bloom</t>
+          <t>Tacetite Bloom tiêu chuẩn</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Dũng khí của Feilian</t>
+          <t>Dũng khí của Phi Liên</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Guardian's Promise</t>
+          <t>Lời Hứa Người Bảo Vệ</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Power Hammer</t>
+          <t>Búa Năng Lượng</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Trái tim Cơ khí</t>
+          <t>Trái Tim Bánh Răng</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Cái giá của Sự Phá hủy</t>
+          <t>Giá Trị của Sự Hủy Diệt</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Moderately Mutated Structure</t>
+          <t>Cấu Trúc Đột Biến Mức Trung Bình</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Captain's Dog Tag</t>
+          <t>Thẻ bài của Đại úy</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Bảng Tên Vô Danh</t>
+          <t>Bảng tên của Những Kẻ Vô Danh</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Cành cây Dưới Đáy Biển</t>
+          <t>Nhánh Dưới Đáy Biển</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Elastic Spring</t>
+          <t>Lò Xo Đàn Hồi</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Brilliant Tacetite Bloom</t>
+          <t>Đóa Tacetite Rực Rỡ</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Guardian's Pledge</t>
+          <t>Lời Thề Người Bảo Vệ</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Vật phẩm không đủ để giải mã</t>
+          <t>Không đủ vật phẩm để giải mã</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>TD bị đánh bại</t>
+          <t>Tacet Discord bị đánh bại</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Resonator Ascension Planner</t>
+          <t>Công Cụ Lên Kế Hoạch Thăng Cấp Resonator</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Ascension Planner</t>
+          <t>Lộ trình thăng hoa</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Weapons</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Echoes</t>
+          <t>Echo</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Resonator Nâng cấp</t>
+          <t>Nâng Cấp Resonator</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Weapon Nâng cấp</t>
+          <t>Nâng Cấp Vũ Khí</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Weapon Recommendations</t>
+          <t>Danh Sách Gợi Ý Vũ Khí</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Echoes Nâng cấp</t>
+          <t>Nâng Cấp Echo</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Echo Recommendations</t>
+          <t>Các Gợi Ý Tần Số</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Skills Nâng cấp - Basic</t>
+          <t>Nâng cấp kỹ năng - Cơ bản</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Skills Nâng cấp - Complete</t>
+          <t>Nâng cấp kỹ năng - Hoàn chỉnh</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Show Basic Plan</t>
+          <t>Hiển thị Kế hoạch Cơ bản</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Show Complete Plan</t>
+          <t>Hiển thị Kế hoạch Hoàn chỉnh</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Chuyển đổi</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Hiện không thể nhận được</t>
+          <t>Hiện chưa thể nhận được</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Triệu Tập</t>
+          <t>Triệu tập</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Crafting</t>
+          <t>Đang chế tác</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Podcast Pioneer</t>
+          <t>Podcast Tiên Phong</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Quests</t>
+          <t>Nhiệm vụ</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Switch Plan</t>
+          <t>Chuyển Kế Hoạch</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Switch Plan</t>
+          <t>Chuyển Kế Hoạch</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Kế hoạch đã được chọn</t>
+          <t>Kế Hoạch đã được chọn trước đó</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Đã đạt cấp độ tối đa</t>
+          <t>Đã đạt cấp tối đa</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Chưa Sở Hữu</t>
+          <t>Không sở hữu</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Đạt cấp tối đa</t>
+          <t>Đã đạt cấp tối đa</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>COST 4</t>
+          <t>CHI PHÍ 4</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Vật liệu EXP Resonator</t>
+          <t>Vật Liệu Kinh Nghiệm Resonator</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Vật liệu EXP Vũ khí</t>
+          <t>Vật liệu Tăng EXP Vũ Khí</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Vật liệu Thăng hoa</t>
+          <t>Vật liệu thăng hoa</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Vật liệu Thăng hoa Resonator</t>
+          <t>Vật liệu Tiến Hóa Resonator</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Loại Vũ khí: Broadblade</t>
+          <t>Loại Vũ Khí: Kiếm Rộng</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Loại Vũ khí: Kiếm</t>
+          <t>Loại Vũ Khí: Kiếm</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Loại Vũ khí: Pistols</t>
+          <t>Loại Vũ Khí: Súng Ngắn</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Loại Vũ khí: Gauntlets</t>
+          <t>Loại Vũ Khí: Quả Cầu Sắt</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Loại Vũ khí: Rectifier</t>
+          <t>Loại Vũ Khí: Bộ Chỉnh Lưu</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Đã đạt cấp độ tối đa</t>
+          <t>Đã đạt cấp tối đa</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Popular Weapons</t>
+          <t>Vũ khí được ưa chuộng</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Unpinned</t>
+          <t>Thoát Khỏi Xiềng Xích</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Not Yet Unlocked</t>
+          <t>Chưa mở khóa</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Phantom Unlogged</t>
+          <t>Ảo Giác Vô Danh</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Melody Orchestration</t>
+          <t>Bản Hòa Tấu Giai Điệu</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Triptych Chests</t>
+          <t>Rương Ba Mảnh</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Nightmare Purification</t>
+          <t>Thanh Tẩy Ác Mộng</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Pipe Maintanence</t>
+          <t>Bảo trì Đường ống</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Default</t>
+          <t>Mặc định</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Weapon Thư viện</t>
+          <t>Bộ Sưu Tập Vũ Khí</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Weapon Projection Thư viện</t>
+          <t>Bộ Sưu Tập Hình Ảnh Vũ Khí</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Controller: Cursor Magnetism</t>
+          <t>Bộ điều khiển: Từ hóa Con trỏ</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Fabricatorium of the Deep: Báo cáo Giám sát I</t>
+          <t>Fabricatorium Vực Sâu: Báo Cáo Giám Sát I</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Fabricatorium of the Deep: Báo cáo Giám sát II</t>
+          <t>Fabricatorium Vực Sâu: Báo Cáo Giám Sát II</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Eternal Blazing Sun</t>
+          <t>Mặt Trời Rực Cháy Vĩnh Cửu</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Đi Sâu Vào Bụi Rậm</t>
+          <t>Vào Rừng Rậm</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Waiting Game</t>
+          <t>Trò chờ đợi</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Đối Mặt</t>
+          <t>Đối Mặt Trực Diện</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Encirclement</t>
+          <t>Bao Vây</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>The Runaway</t>
+          <t>Kẻ Đào Tẩu</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Hidden Tracks</t>
+          <t>Những Dấu Vết Bí Ẩn</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Kết Thúc Cuộc Săn</t>
+          <t>Kết thúc Cuộc săn</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Dễ thôi</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Khó</t>
+          <t>Khó khăn</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Expert</t>
+          <t>Chuyên Gia</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Expert</t>
+          <t>Chuyên Gia</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Đi Sâu Vào Bụi Rậm: Dễ</t>
+          <t>Vào Rừng Rậm: Dễ</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Đi Sâu Vào Bụi Rậm: Khó</t>
+          <t>Vào Rừng Rậm: Khó</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Đi Sâu Vào Bụi Rậm: Chuyên Gia</t>
+          <t>Vào Rừng Rậm: Cao Thủ</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Waiting Game: Easy</t>
+          <t>Trò chờ đợi: Dễ</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Waiting Game: Khó</t>
+          <t>Trò chờ đợi: Khó</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Waiting Game: Expert</t>
+          <t>Trò chờ đợi: Cao thủ</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Đối Mặt: Dễ</t>
+          <t>Đối Mặt Trực Diện: Dễ</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Đối Mặt: Khó</t>
+          <t>Đối Mặt Trực Diện: Khó</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Đối Mặt: Chuyên Gia</t>
+          <t>Đối Mặt Trực Diện: Cao Thủ</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Encirclement: Easy</t>
+          <t>Bao Vây: Dễ</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Encirclement: Khó</t>
+          <t>Bao Vây: Khó</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Encirclement: Expert</t>
+          <t>Bao Vây: Cao Thủ</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>The Runaway: Easy</t>
+          <t>Kẻ Đào Tẩu: Dễ</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>The Runaway: Khó</t>
+          <t>Kẻ Đào Tẩu: Khó</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>The Runaway: Expert</t>
+          <t>Kẻ Đào Tẩu: Cao Thủ</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Hidden Tracks: Easy</t>
+          <t>Những Dấu Vết Bí Ẩn: Dễ</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Hidden Tracks: Khó</t>
+          <t>Những Dấu Vết Bí Ẩn: Khó</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Hidden Tracks: Expert</t>
+          <t>Những Dấu Vết Bí Ẩn: Cao Thủ</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Kết Thúc Cuộc Săn: Dễ</t>
+          <t>Kết thúc Cuộc săn: Dễ</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Kết Thúc Cuộc Săn: Khó</t>
+          <t>Săn Bắt Cuối Cùng: Khó</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Kết Thúc Cuộc Săn: Chuyên Gia</t>
+          <t>Kết thúc Cuộc săn: Cao thủ</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Gửi Những Anh Hùng...</t>
+          <t>Tới Những Người Anh Hùng...</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Hoàn thành cuộc săn đầu tiên trong Nhiệm Vụ Chính "Bằng Bàn Tay Cháy Bỏng Của Mặt Trời"</t>
+          <t>Hoàn thành cuộc săn đầu tiên trong Nhiệm Vụ Chính "By Sun's Burning Hand"</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Lựa Chọn</t>
+          <t>Chọn</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Lựa Chọn Chiến Thuật</t>
+          <t>Chọn Các Chiến Thuật</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Địa hình trong khu vực đã thay đổi</t>
+          <t>Địa hình trong khu vực đã thay đổi.</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Enhance</t>
+          <t>Tăng cường</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Tự Động Hóa, Con Trai!</t>
+          <t>Máy tự động, con trai!</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Họ Call Me TD Terminator</t>
+          <t>Chúng Gọi Ta Là Sát Thủ TD</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>"Đừng Giận Tôi Nhé, Hả?"</t>
+          <t>"Đừng Giận Tớ Nhé, Hả?"</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Lister the Tormentor</t>
+          <t>Kẻ Tra Tấn Đau Khổ</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Cẩn Thận, Cẩn Thận...</t>
+          <t>Cẩn thận... Cẩn thận...</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
